--- a/salidas/empresas/HOOD.xlsx
+++ b/salidas/empresas/HOOD.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mensual" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="EPS" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Acciones" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Info" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Mensual" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="EPS" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Acciones" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Info" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -23,13 +23,16 @@
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD"/>
   </numFmts>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -40,7 +43,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -48,12 +51,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -435,54 +447,54 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>fecha</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>precio_ajustado</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>precio_cierre</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>volumen</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>eps_ttm</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>pe</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>acciones_circulacion</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>market_cap</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>rotacion</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>44408</v>
       </c>
       <c r="B2" t="n">
@@ -501,7 +513,7 @@
       <c r="I2" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>44439</v>
       </c>
       <c r="B3" t="n">
@@ -526,7 +538,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>44469</v>
       </c>
       <c r="B4" t="n">
@@ -551,7 +563,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>44500</v>
       </c>
       <c r="B5" t="n">
@@ -576,7 +588,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>44530</v>
       </c>
       <c r="B6" t="n">
@@ -601,7 +613,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>44561</v>
       </c>
       <c r="B7" t="n">
@@ -626,7 +638,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>44592</v>
       </c>
       <c r="B8" t="n">
@@ -651,7 +663,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>44620</v>
       </c>
       <c r="B9" t="n">
@@ -676,7 +688,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>44651</v>
       </c>
       <c r="B10" t="n">
@@ -701,7 +713,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>44681</v>
       </c>
       <c r="B11" t="n">
@@ -726,7 +738,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>44712</v>
       </c>
       <c r="B12" t="n">
@@ -751,7 +763,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>44742</v>
       </c>
       <c r="B13" t="n">
@@ -776,7 +788,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>44773</v>
       </c>
       <c r="B14" t="n">
@@ -801,7 +813,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>44804</v>
       </c>
       <c r="B15" t="n">
@@ -826,7 +838,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>44834</v>
       </c>
       <c r="B16" t="n">
@@ -851,7 +863,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>44865</v>
       </c>
       <c r="B17" t="n">
@@ -876,7 +888,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>44895</v>
       </c>
       <c r="B18" t="n">
@@ -901,7 +913,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>44926</v>
       </c>
       <c r="B19" t="n">
@@ -926,7 +938,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>44957</v>
       </c>
       <c r="B20" t="n">
@@ -951,7 +963,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>44985</v>
       </c>
       <c r="B21" t="n">
@@ -978,7 +990,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>45016</v>
       </c>
       <c r="B22" t="n">
@@ -1005,7 +1017,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>45046</v>
       </c>
       <c r="B23" t="n">
@@ -1032,7 +1044,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>45077</v>
       </c>
       <c r="B24" t="n">
@@ -1059,7 +1071,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>45107</v>
       </c>
       <c r="B25" t="n">
@@ -1086,7 +1098,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>45138</v>
       </c>
       <c r="B26" t="n">
@@ -1113,7 +1125,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>45169</v>
       </c>
       <c r="B27" t="n">
@@ -1140,7 +1152,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>45199</v>
       </c>
       <c r="B28" t="n">
@@ -1167,7 +1179,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>45230</v>
       </c>
       <c r="B29" t="n">
@@ -1194,7 +1206,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>45260</v>
       </c>
       <c r="B30" t="n">
@@ -1221,7 +1233,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>45291</v>
       </c>
       <c r="B31" t="n">
@@ -1248,7 +1260,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>45322</v>
       </c>
       <c r="B32" t="n">
@@ -1275,7 +1287,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>45351</v>
       </c>
       <c r="B33" t="n">
@@ -1302,7 +1314,7 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>45382</v>
       </c>
       <c r="B34" t="n">
@@ -1329,7 +1341,7 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>45412</v>
       </c>
       <c r="B35" t="n">
@@ -1356,7 +1368,7 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>45443</v>
       </c>
       <c r="B36" t="n">
@@ -1385,7 +1397,7 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>45473</v>
       </c>
       <c r="B37" t="n">
@@ -1414,7 +1426,7 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>45504</v>
       </c>
       <c r="B38" t="n">
@@ -1443,7 +1455,7 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>45535</v>
       </c>
       <c r="B39" t="n">
@@ -1472,7 +1484,7 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>45565</v>
       </c>
       <c r="B40" t="n">
@@ -1501,7 +1513,7 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>45596</v>
       </c>
       <c r="B41" t="n">
@@ -1530,7 +1542,7 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>45626</v>
       </c>
       <c r="B42" t="n">
@@ -1559,7 +1571,7 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>45657</v>
       </c>
       <c r="B43" t="n">
@@ -1588,7 +1600,7 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>45688</v>
       </c>
       <c r="B44" t="n">
@@ -1617,7 +1629,7 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>45716</v>
       </c>
       <c r="B45" t="n">
@@ -1646,7 +1658,7 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>45747</v>
       </c>
       <c r="B46" t="n">
@@ -1675,7 +1687,7 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>45777</v>
       </c>
       <c r="B47" t="n">
@@ -1704,7 +1716,7 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>45808</v>
       </c>
       <c r="B48" t="n">
@@ -1733,7 +1745,7 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>45838</v>
       </c>
       <c r="B49" t="n">
@@ -1762,7 +1774,7 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>45869</v>
       </c>
       <c r="B50" t="n">
@@ -1791,7 +1803,7 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>45900</v>
       </c>
       <c r="B51" t="n">
@@ -1820,7 +1832,7 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>45930</v>
       </c>
       <c r="B52" t="n">
@@ -1849,7 +1861,7 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>45961</v>
       </c>
       <c r="B53" t="n">
@@ -1878,7 +1890,7 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>45991</v>
       </c>
       <c r="B54" t="n">
@@ -1907,7 +1919,7 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>46022</v>
       </c>
       <c r="B55" t="n">
@@ -1936,7 +1948,7 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>46053</v>
       </c>
       <c r="B56" t="n">
@@ -1965,7 +1977,7 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>46081</v>
       </c>
       <c r="B57" t="n">
@@ -1994,7 +2006,7 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>46112</v>
       </c>
       <c r="B58" t="n">
@@ -2023,7 +2035,7 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>46142</v>
       </c>
       <c r="B59" t="n">
@@ -2052,7 +2064,7 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>46173</v>
       </c>
       <c r="B60" t="n">
@@ -2081,7 +2093,7 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>46203</v>
       </c>
       <c r="B61" t="n">
@@ -2110,7 +2122,7 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>46234</v>
       </c>
       <c r="B62" t="n">
@@ -2139,7 +2151,7 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>46265</v>
       </c>
       <c r="B63" t="n">
@@ -2168,32 +2180,32 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" s="2" t="n">
         <v>46295</v>
       </c>
       <c r="B64" t="n">
-        <v>122.6999969482422</v>
+        <v>120.8199996948242</v>
       </c>
       <c r="C64" t="n">
-        <v>122.6999969482422</v>
+        <v>120.8199996948242</v>
       </c>
       <c r="D64" t="n">
-        <v>400014200</v>
+        <v>415013000</v>
       </c>
       <c r="E64" t="n">
         <v>2.26</v>
       </c>
       <c r="F64" t="n">
-        <v>54.29203404789478</v>
+        <v>53.46017685611692</v>
       </c>
       <c r="G64" t="n">
         <v>899000000</v>
       </c>
       <c r="H64" t="n">
-        <v>110307297256.4697</v>
+        <v>108617179725.647</v>
       </c>
       <c r="I64" t="n">
-        <v>0.4449546162402669</v>
+        <v>0.4616384872080089</v>
       </c>
     </row>
   </sheetData>
@@ -2225,75 +2237,75 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>start</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>end</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>filed</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>form</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>fy</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>fp</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>eps_trimestral</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>origen</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>eps_ttm</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>filed_ttm</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>factor</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>tag</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>43922</v>
       </c>
-      <c r="B2" s="1" t="n">
+      <c r="B2" s="2" t="n">
         <v>44012</v>
       </c>
-      <c r="C2" s="1" t="n">
+      <c r="C2" s="2" t="n">
         <v>44426</v>
       </c>
       <c r="D2" t="inlineStr">
@@ -2329,13 +2341,13 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>44013</v>
       </c>
-      <c r="B3" s="1" t="n">
+      <c r="B3" s="2" t="n">
         <v>44104</v>
       </c>
-      <c r="C3" s="1" t="n">
+      <c r="C3" s="2" t="n">
         <v>44498</v>
       </c>
       <c r="D3" t="inlineStr">
@@ -2371,13 +2383,13 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>44197</v>
       </c>
-      <c r="B4" s="1" t="n">
+      <c r="B4" s="2" t="n">
         <v>44286</v>
       </c>
-      <c r="C4" s="1" t="n">
+      <c r="C4" s="2" t="n">
         <v>44687</v>
       </c>
       <c r="D4" t="inlineStr">
@@ -2413,13 +2425,13 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>44287</v>
       </c>
-      <c r="B5" s="1" t="n">
+      <c r="B5" s="2" t="n">
         <v>44377</v>
       </c>
-      <c r="C5" s="1" t="n">
+      <c r="C5" s="2" t="n">
         <v>44426</v>
       </c>
       <c r="D5" t="inlineStr">
@@ -2455,13 +2467,13 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>44378</v>
       </c>
-      <c r="B6" s="1" t="n">
+      <c r="B6" s="2" t="n">
         <v>44469</v>
       </c>
-      <c r="C6" s="1" t="n">
+      <c r="C6" s="2" t="n">
         <v>44498</v>
       </c>
       <c r="D6" t="inlineStr">
@@ -2497,13 +2509,13 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>44562</v>
       </c>
-      <c r="B7" s="1" t="n">
+      <c r="B7" s="2" t="n">
         <v>44651</v>
       </c>
-      <c r="C7" s="1" t="n">
+      <c r="C7" s="2" t="n">
         <v>44687</v>
       </c>
       <c r="D7" t="inlineStr">
@@ -2539,13 +2551,13 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>44652</v>
       </c>
-      <c r="B8" s="1" t="n">
+      <c r="B8" s="2" t="n">
         <v>44742</v>
       </c>
-      <c r="C8" s="1" t="n">
+      <c r="C8" s="2" t="n">
         <v>44776</v>
       </c>
       <c r="D8" t="inlineStr">
@@ -2581,13 +2593,13 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>44743</v>
       </c>
-      <c r="B9" s="1" t="n">
+      <c r="B9" s="2" t="n">
         <v>44834</v>
       </c>
-      <c r="C9" s="1" t="n">
+      <c r="C9" s="2" t="n">
         <v>44868</v>
       </c>
       <c r="D9" t="inlineStr">
@@ -2623,13 +2635,13 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>44835</v>
       </c>
-      <c r="B10" s="1" t="n">
+      <c r="B10" s="2" t="n">
         <v>44926</v>
       </c>
-      <c r="C10" s="1" t="n">
+      <c r="C10" s="2" t="n">
         <v>44984</v>
       </c>
       <c r="D10" t="inlineStr">
@@ -2656,7 +2668,7 @@
       <c r="I10" t="n">
         <v>-1.17</v>
       </c>
-      <c r="J10" s="1" t="n">
+      <c r="J10" s="2" t="n">
         <v>44984</v>
       </c>
       <c r="K10" t="n">
@@ -2669,13 +2681,13 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>44927</v>
       </c>
-      <c r="B11" s="1" t="n">
+      <c r="B11" s="2" t="n">
         <v>45016</v>
       </c>
-      <c r="C11" s="1" t="n">
+      <c r="C11" s="2" t="n">
         <v>45056</v>
       </c>
       <c r="D11" t="inlineStr">
@@ -2702,7 +2714,7 @@
       <c r="I11" t="n">
         <v>-1.29</v>
       </c>
-      <c r="J11" s="1" t="n">
+      <c r="J11" s="2" t="n">
         <v>45056</v>
       </c>
       <c r="K11" t="n">
@@ -2715,13 +2727,13 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>45017</v>
       </c>
-      <c r="B12" s="1" t="n">
+      <c r="B12" s="2" t="n">
         <v>45107</v>
       </c>
-      <c r="C12" s="1" t="n">
+      <c r="C12" s="2" t="n">
         <v>45141</v>
       </c>
       <c r="D12" t="inlineStr">
@@ -2748,7 +2760,7 @@
       <c r="I12" t="n">
         <v>-0.9199999999999999</v>
       </c>
-      <c r="J12" s="1" t="n">
+      <c r="J12" s="2" t="n">
         <v>45141</v>
       </c>
       <c r="K12" t="n">
@@ -2761,13 +2773,13 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>45108</v>
       </c>
-      <c r="B13" s="1" t="n">
+      <c r="B13" s="2" t="n">
         <v>45199</v>
       </c>
-      <c r="C13" s="1" t="n">
+      <c r="C13" s="2" t="n">
         <v>45237</v>
       </c>
       <c r="D13" t="inlineStr">
@@ -2794,7 +2806,7 @@
       <c r="I13" t="n">
         <v>-0.8100000000000001</v>
       </c>
-      <c r="J13" s="1" t="n">
+      <c r="J13" s="2" t="n">
         <v>45237</v>
       </c>
       <c r="K13" t="n">
@@ -2807,13 +2819,13 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>45200</v>
       </c>
-      <c r="B14" s="1" t="n">
+      <c r="B14" s="2" t="n">
         <v>45291</v>
       </c>
-      <c r="C14" s="1" t="n">
+      <c r="C14" s="2" t="n">
         <v>45349</v>
       </c>
       <c r="D14" t="inlineStr">
@@ -2840,7 +2852,7 @@
       <c r="I14" t="n">
         <v>-0.6100000000000001</v>
       </c>
-      <c r="J14" s="1" t="n">
+      <c r="J14" s="2" t="n">
         <v>45349</v>
       </c>
       <c r="K14" t="n">
@@ -2853,13 +2865,13 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>45292</v>
       </c>
-      <c r="B15" s="1" t="n">
+      <c r="B15" s="2" t="n">
         <v>45382</v>
       </c>
-      <c r="C15" s="1" t="n">
+      <c r="C15" s="2" t="n">
         <v>45420</v>
       </c>
       <c r="D15" t="inlineStr">
@@ -2886,7 +2898,7 @@
       <c r="I15" t="n">
         <v>0.1399999999999999</v>
       </c>
-      <c r="J15" s="1" t="n">
+      <c r="J15" s="2" t="n">
         <v>45420</v>
       </c>
       <c r="K15" t="n">
@@ -2899,13 +2911,13 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>45383</v>
       </c>
-      <c r="B16" s="1" t="n">
+      <c r="B16" s="2" t="n">
         <v>45473</v>
       </c>
-      <c r="C16" s="1" t="n">
+      <c r="C16" s="2" t="n">
         <v>45512</v>
       </c>
       <c r="D16" t="inlineStr">
@@ -2932,7 +2944,7 @@
       <c r="I16" t="n">
         <v>0.3199999999999999</v>
       </c>
-      <c r="J16" s="1" t="n">
+      <c r="J16" s="2" t="n">
         <v>45512</v>
       </c>
       <c r="K16" t="n">
@@ -2945,13 +2957,13 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>45474</v>
       </c>
-      <c r="B17" s="1" t="n">
+      <c r="B17" s="2" t="n">
         <v>45565</v>
       </c>
-      <c r="C17" s="1" t="n">
+      <c r="C17" s="2" t="n">
         <v>45596</v>
       </c>
       <c r="D17" t="inlineStr">
@@ -2978,7 +2990,7 @@
       <c r="I17" t="n">
         <v>0.58</v>
       </c>
-      <c r="J17" s="1" t="n">
+      <c r="J17" s="2" t="n">
         <v>45596</v>
       </c>
       <c r="K17" t="n">
@@ -2991,13 +3003,13 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>45566</v>
       </c>
-      <c r="B18" s="1" t="n">
+      <c r="B18" s="2" t="n">
         <v>45657</v>
       </c>
-      <c r="C18" s="1" t="n">
+      <c r="C18" s="2" t="n">
         <v>45706</v>
       </c>
       <c r="D18" t="inlineStr">
@@ -3024,7 +3036,7 @@
       <c r="I18" t="n">
         <v>1.56</v>
       </c>
-      <c r="J18" s="1" t="n">
+      <c r="J18" s="2" t="n">
         <v>45706</v>
       </c>
       <c r="K18" t="n">
@@ -3037,13 +3049,13 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>45658</v>
       </c>
-      <c r="B19" s="1" t="n">
+      <c r="B19" s="2" t="n">
         <v>45747</v>
       </c>
-      <c r="C19" s="1" t="n">
+      <c r="C19" s="2" t="n">
         <v>45778</v>
       </c>
       <c r="D19" t="inlineStr">
@@ -3070,7 +3082,7 @@
       <c r="I19" t="n">
         <v>1.75</v>
       </c>
-      <c r="J19" s="1" t="n">
+      <c r="J19" s="2" t="n">
         <v>45778</v>
       </c>
       <c r="K19" t="n">
@@ -3083,13 +3095,13 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>45748</v>
       </c>
-      <c r="B20" s="1" t="n">
+      <c r="B20" s="2" t="n">
         <v>45838</v>
       </c>
-      <c r="C20" s="1" t="n">
+      <c r="C20" s="2" t="n">
         <v>45869</v>
       </c>
       <c r="D20" t="inlineStr">
@@ -3116,7 +3128,7 @@
       <c r="I20" t="n">
         <v>1.96</v>
       </c>
-      <c r="J20" s="1" t="n">
+      <c r="J20" s="2" t="n">
         <v>45869</v>
       </c>
       <c r="K20" t="n">
@@ -3129,13 +3141,13 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>45839</v>
       </c>
-      <c r="B21" s="1" t="n">
+      <c r="B21" s="2" t="n">
         <v>45930</v>
       </c>
-      <c r="C21" s="1" t="n">
+      <c r="C21" s="2" t="n">
         <v>45967</v>
       </c>
       <c r="D21" t="inlineStr">
@@ -3162,7 +3174,7 @@
       <c r="I21" t="n">
         <v>2.4</v>
       </c>
-      <c r="J21" s="1" t="n">
+      <c r="J21" s="2" t="n">
         <v>45967</v>
       </c>
       <c r="K21" t="n">
@@ -3175,13 +3187,13 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>45931</v>
       </c>
-      <c r="B22" s="1" t="n">
+      <c r="B22" s="2" t="n">
         <v>46022</v>
       </c>
-      <c r="C22" s="1" t="n">
+      <c r="C22" s="2" t="n">
         <v>46071</v>
       </c>
       <c r="D22" t="inlineStr">
@@ -3208,7 +3220,7 @@
       <c r="I22" t="n">
         <v>2.05</v>
       </c>
-      <c r="J22" s="1" t="n">
+      <c r="J22" s="2" t="n">
         <v>46071</v>
       </c>
       <c r="K22" t="n">
@@ -3221,13 +3233,13 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>46023</v>
       </c>
-      <c r="B23" s="1" t="n">
+      <c r="B23" s="2" t="n">
         <v>46112</v>
       </c>
-      <c r="C23" s="1" t="n">
+      <c r="C23" s="2" t="n">
         <v>46141</v>
       </c>
       <c r="D23" t="inlineStr">
@@ -3254,7 +3266,7 @@
       <c r="I23" t="n">
         <v>2.06</v>
       </c>
-      <c r="J23" s="1" t="n">
+      <c r="J23" s="2" t="n">
         <v>46141</v>
       </c>
       <c r="K23" t="n">
@@ -3267,13 +3279,13 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>46113</v>
       </c>
-      <c r="B24" s="1" t="n">
+      <c r="B24" s="2" t="n">
         <v>46203</v>
       </c>
-      <c r="C24" s="1" t="n">
+      <c r="C24" s="2" t="n">
         <v>46233</v>
       </c>
       <c r="D24" t="inlineStr">
@@ -3300,7 +3312,7 @@
       <c r="I24" t="n">
         <v>2.26</v>
       </c>
-      <c r="J24" s="1" t="n">
+      <c r="J24" s="2" t="n">
         <v>46233</v>
       </c>
       <c r="K24" t="n">
@@ -3338,57 +3350,57 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>end</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>filed</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>acciones</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>form</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>fy</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>fp</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>tag</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>origen</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>factor</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>44012</v>
       </c>
-      <c r="B2" s="1" t="n">
+      <c r="B2" s="2" t="n">
         <v>44426</v>
       </c>
       <c r="C2" t="n">
@@ -3422,10 +3434,10 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>44377</v>
       </c>
-      <c r="B3" s="1" t="n">
+      <c r="B3" s="2" t="n">
         <v>44426</v>
       </c>
       <c r="C3" t="n">
@@ -3459,10 +3471,10 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>44104</v>
       </c>
-      <c r="B4" s="1" t="n">
+      <c r="B4" s="2" t="n">
         <v>44498</v>
       </c>
       <c r="C4" t="n">
@@ -3496,10 +3508,10 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>43830</v>
       </c>
-      <c r="B5" s="1" t="n">
+      <c r="B5" s="2" t="n">
         <v>44616</v>
       </c>
       <c r="C5" t="n">
@@ -3533,10 +3545,10 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>44196</v>
       </c>
-      <c r="B6" s="1" t="n">
+      <c r="B6" s="2" t="n">
         <v>44616</v>
       </c>
       <c r="C6" t="n">
@@ -3570,10 +3582,10 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>44286</v>
       </c>
-      <c r="B7" s="1" t="n">
+      <c r="B7" s="2" t="n">
         <v>44687</v>
       </c>
       <c r="C7" t="n">
@@ -3607,10 +3619,10 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>44651</v>
       </c>
-      <c r="B8" s="1" t="n">
+      <c r="B8" s="2" t="n">
         <v>44687</v>
       </c>
       <c r="C8" t="n">
@@ -3644,10 +3656,10 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>44742</v>
       </c>
-      <c r="B9" s="1" t="n">
+      <c r="B9" s="2" t="n">
         <v>44776</v>
       </c>
       <c r="C9" t="n">
@@ -3681,10 +3693,10 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>44834</v>
       </c>
-      <c r="B10" s="1" t="n">
+      <c r="B10" s="2" t="n">
         <v>44868</v>
       </c>
       <c r="C10" t="n">
@@ -3718,10 +3730,10 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>44926</v>
       </c>
-      <c r="B11" s="1" t="n">
+      <c r="B11" s="2" t="n">
         <v>44984</v>
       </c>
       <c r="C11" t="n">
@@ -3755,10 +3767,10 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>45016</v>
       </c>
-      <c r="B12" s="1" t="n">
+      <c r="B12" s="2" t="n">
         <v>45056</v>
       </c>
       <c r="C12" t="n">
@@ -3792,10 +3804,10 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>45107</v>
       </c>
-      <c r="B13" s="1" t="n">
+      <c r="B13" s="2" t="n">
         <v>45141</v>
       </c>
       <c r="C13" t="n">
@@ -3829,10 +3841,10 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>45199</v>
       </c>
-      <c r="B14" s="1" t="n">
+      <c r="B14" s="2" t="n">
         <v>45237</v>
       </c>
       <c r="C14" t="n">
@@ -3866,10 +3878,10 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>45291</v>
       </c>
-      <c r="B15" s="1" t="n">
+      <c r="B15" s="2" t="n">
         <v>45349</v>
       </c>
       <c r="C15" t="n">
@@ -3903,10 +3915,10 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>45382</v>
       </c>
-      <c r="B16" s="1" t="n">
+      <c r="B16" s="2" t="n">
         <v>45420</v>
       </c>
       <c r="C16" t="n">
@@ -3940,10 +3952,10 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>45473</v>
       </c>
-      <c r="B17" s="1" t="n">
+      <c r="B17" s="2" t="n">
         <v>45512</v>
       </c>
       <c r="C17" t="n">
@@ -3977,10 +3989,10 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>45565</v>
       </c>
-      <c r="B18" s="1" t="n">
+      <c r="B18" s="2" t="n">
         <v>45596</v>
       </c>
       <c r="C18" t="n">
@@ -4014,10 +4026,10 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>45657</v>
       </c>
-      <c r="B19" s="1" t="n">
+      <c r="B19" s="2" t="n">
         <v>45706</v>
       </c>
       <c r="C19" t="n">
@@ -4051,10 +4063,10 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>45747</v>
       </c>
-      <c r="B20" s="1" t="n">
+      <c r="B20" s="2" t="n">
         <v>45778</v>
       </c>
       <c r="C20" t="n">
@@ -4088,10 +4100,10 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>45838</v>
       </c>
-      <c r="B21" s="1" t="n">
+      <c r="B21" s="2" t="n">
         <v>45869</v>
       </c>
       <c r="C21" t="n">
@@ -4125,10 +4137,10 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>45930</v>
       </c>
-      <c r="B22" s="1" t="n">
+      <c r="B22" s="2" t="n">
         <v>45967</v>
       </c>
       <c r="C22" t="n">
@@ -4162,10 +4174,10 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>46022</v>
       </c>
-      <c r="B23" s="1" t="n">
+      <c r="B23" s="2" t="n">
         <v>46071</v>
       </c>
       <c r="C23" t="n">
@@ -4199,10 +4211,10 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>46112</v>
       </c>
-      <c r="B24" s="1" t="n">
+      <c r="B24" s="2" t="n">
         <v>46141</v>
       </c>
       <c r="C24" t="n">
@@ -4236,10 +4248,10 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>46203</v>
       </c>
-      <c r="B25" s="1" t="n">
+      <c r="B25" s="2" t="n">
         <v>46233</v>
       </c>
       <c r="C25" t="n">
@@ -4291,12 +4303,12 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>campo</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>valor</t>
         </is>
